--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368303</v>
+        <v>121369125</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>57364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,49 +1023,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581122</v>
+        <v>581021</v>
       </c>
       <c r="R5" t="n">
-        <v>6388098</v>
+        <v>6388049</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121369125</v>
+        <v>121368303</v>
       </c>
       <c r="B6" t="n">
-        <v>57364</v>
+        <v>98071</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,53 +1137,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581021</v>
+        <v>581122</v>
       </c>
       <c r="R6" t="n">
-        <v>6388049</v>
+        <v>6388098</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121368704</v>
+        <v>121369125</v>
       </c>
       <c r="B2" t="n">
-        <v>105176</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581129</v>
+        <v>581021</v>
       </c>
       <c r="R2" t="n">
-        <v>6388103</v>
+        <v>6388049</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368155</v>
+        <v>121368303</v>
       </c>
       <c r="B3" t="n">
-        <v>105176</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581151</v>
+        <v>581122</v>
       </c>
       <c r="R3" t="n">
-        <v>6388061</v>
+        <v>6388098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121367964</v>
+        <v>121368704</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>105186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,45 +916,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581144</v>
+        <v>581129</v>
       </c>
       <c r="R4" t="n">
-        <v>6388089</v>
+        <v>6388103</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121369125</v>
+        <v>121368155</v>
       </c>
       <c r="B5" t="n">
-        <v>57364</v>
+        <v>105186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,53 +1023,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581021</v>
+        <v>581151</v>
       </c>
       <c r="R5" t="n">
-        <v>6388049</v>
+        <v>6388061</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121368303</v>
+        <v>121367964</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>92006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,46 +1134,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581122</v>
+        <v>581144</v>
       </c>
       <c r="R6" t="n">
-        <v>6388098</v>
+        <v>6388089</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>121368240</v>
       </c>
       <c r="B7" t="n">
-        <v>94690</v>
+        <v>94700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121369125</v>
+        <v>121368303</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581021</v>
+        <v>581122</v>
       </c>
       <c r="R2" t="n">
-        <v>6388049</v>
+        <v>6388098</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368303</v>
+        <v>121368155</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581122</v>
+        <v>581151</v>
       </c>
       <c r="R3" t="n">
-        <v>6388098</v>
+        <v>6388061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368704</v>
+        <v>121369125</v>
       </c>
       <c r="B4" t="n">
-        <v>105186</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +909,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581129</v>
+        <v>581021</v>
       </c>
       <c r="R4" t="n">
-        <v>6388103</v>
+        <v>6388049</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368155</v>
+        <v>121367964</v>
       </c>
       <c r="B5" t="n">
-        <v>105186</v>
+        <v>92006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,42 +1027,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581151</v>
+        <v>581144</v>
       </c>
       <c r="R5" t="n">
-        <v>6388061</v>
+        <v>6388089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121367964</v>
+        <v>121368704</v>
       </c>
       <c r="B6" t="n">
-        <v>92006</v>
+        <v>105186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,45 +1141,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581144</v>
+        <v>581129</v>
       </c>
       <c r="R6" t="n">
-        <v>6388089</v>
+        <v>6388103</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121368303</v>
+        <v>121369125</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581122</v>
+        <v>581021</v>
       </c>
       <c r="R2" t="n">
-        <v>6388098</v>
+        <v>6388049</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368155</v>
+        <v>121367964</v>
       </c>
       <c r="B3" t="n">
-        <v>105186</v>
+        <v>92018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,42 +805,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581151</v>
+        <v>581144</v>
       </c>
       <c r="R3" t="n">
-        <v>6388061</v>
+        <v>6388089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121369125</v>
+        <v>121368704</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>105199</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581021</v>
+        <v>581129</v>
       </c>
       <c r="R4" t="n">
-        <v>6388049</v>
+        <v>6388103</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121367964</v>
+        <v>121368155</v>
       </c>
       <c r="B5" t="n">
-        <v>92006</v>
+        <v>105199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,45 +1030,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581144</v>
+        <v>581151</v>
       </c>
       <c r="R5" t="n">
-        <v>6388089</v>
+        <v>6388061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121368704</v>
+        <v>121368303</v>
       </c>
       <c r="B6" t="n">
-        <v>105186</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,14 +1169,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581129</v>
+        <v>581122</v>
       </c>
       <c r="R6" t="n">
-        <v>6388103</v>
+        <v>6388098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>121368240</v>
       </c>
       <c r="B7" t="n">
-        <v>94700</v>
+        <v>94712</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121369125</v>
+        <v>121367964</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>92019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581021</v>
+        <v>581144</v>
       </c>
       <c r="R2" t="n">
-        <v>6388049</v>
+        <v>6388089</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121367964</v>
+        <v>121368155</v>
       </c>
       <c r="B3" t="n">
-        <v>92018</v>
+        <v>105200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,45 +805,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581144</v>
+        <v>581151</v>
       </c>
       <c r="R3" t="n">
-        <v>6388089</v>
+        <v>6388061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368704</v>
+        <v>121369125</v>
       </c>
       <c r="B4" t="n">
-        <v>105199</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581129</v>
+        <v>581021</v>
       </c>
       <c r="R4" t="n">
-        <v>6388103</v>
+        <v>6388049</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368155</v>
+        <v>121368704</v>
       </c>
       <c r="B5" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,14 +1058,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581151</v>
+        <v>581129</v>
       </c>
       <c r="R5" t="n">
-        <v>6388061</v>
+        <v>6388103</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1128,7 @@
         <v>121368303</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>121368240</v>
       </c>
       <c r="B7" t="n">
-        <v>94712</v>
+        <v>94713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121367964</v>
+        <v>121369125</v>
       </c>
       <c r="B2" t="n">
-        <v>92019</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581144</v>
+        <v>581021</v>
       </c>
       <c r="R2" t="n">
-        <v>6388089</v>
+        <v>6388049</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368155</v>
+        <v>121368704</v>
       </c>
       <c r="B3" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581151</v>
+        <v>581129</v>
       </c>
       <c r="R3" t="n">
-        <v>6388061</v>
+        <v>6388103</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121369125</v>
+        <v>121368155</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>105203</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,53 +912,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581021</v>
+        <v>581151</v>
       </c>
       <c r="R4" t="n">
-        <v>6388049</v>
+        <v>6388061</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368704</v>
+        <v>121367964</v>
       </c>
       <c r="B5" t="n">
-        <v>105200</v>
+        <v>92022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,42 +1027,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581129</v>
+        <v>581144</v>
       </c>
       <c r="R5" t="n">
-        <v>6388103</v>
+        <v>6388089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1128,7 @@
         <v>121368303</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>121368240</v>
       </c>
       <c r="B7" t="n">
-        <v>94713</v>
+        <v>94716</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121369125</v>
+        <v>121368704</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>105203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581021</v>
+        <v>581129</v>
       </c>
       <c r="R2" t="n">
-        <v>6388049</v>
+        <v>6388103</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368704</v>
+        <v>121369125</v>
       </c>
       <c r="B3" t="n">
-        <v>105203</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581129</v>
+        <v>581021</v>
       </c>
       <c r="R3" t="n">
-        <v>6388103</v>
+        <v>6388049</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121368704</v>
+        <v>121367964</v>
       </c>
       <c r="B2" t="n">
-        <v>105203</v>
+        <v>92028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581129</v>
+        <v>581144</v>
       </c>
       <c r="R2" t="n">
-        <v>6388103</v>
+        <v>6388089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121369125</v>
+        <v>121368704</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>105209</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581021</v>
+        <v>581129</v>
       </c>
       <c r="R3" t="n">
-        <v>6388049</v>
+        <v>6388103</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368155</v>
+        <v>121369125</v>
       </c>
       <c r="B4" t="n">
-        <v>105203</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,49 +912,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581151</v>
+        <v>581021</v>
       </c>
       <c r="R4" t="n">
-        <v>6388061</v>
+        <v>6388049</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121367964</v>
+        <v>121368155</v>
       </c>
       <c r="B5" t="n">
-        <v>92022</v>
+        <v>105209</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,45 +1030,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581144</v>
+        <v>581151</v>
       </c>
       <c r="R5" t="n">
-        <v>6388089</v>
+        <v>6388061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1128,7 @@
         <v>121368303</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>121368240</v>
       </c>
       <c r="B7" t="n">
-        <v>94716</v>
+        <v>94722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121367964</v>
+        <v>121369125</v>
       </c>
       <c r="B2" t="n">
-        <v>92028</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581144</v>
+        <v>581021</v>
       </c>
       <c r="R2" t="n">
-        <v>6388089</v>
+        <v>6388049</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368704</v>
+        <v>121367964</v>
       </c>
       <c r="B3" t="n">
-        <v>105209</v>
+        <v>92029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,42 +805,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581129</v>
+        <v>581144</v>
       </c>
       <c r="R3" t="n">
-        <v>6388103</v>
+        <v>6388089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121369125</v>
+        <v>121368303</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,53 +915,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581021</v>
+        <v>581122</v>
       </c>
       <c r="R4" t="n">
-        <v>6388049</v>
+        <v>6388098</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368155</v>
+        <v>121368704</v>
       </c>
       <c r="B5" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,14 +1058,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581151</v>
+        <v>581129</v>
       </c>
       <c r="R5" t="n">
-        <v>6388061</v>
+        <v>6388103</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121368303</v>
+        <v>121368155</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>105210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581122</v>
+        <v>581151</v>
       </c>
       <c r="R6" t="n">
-        <v>6388098</v>
+        <v>6388061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>121368240</v>
       </c>
       <c r="B7" t="n">
-        <v>94722</v>
+        <v>94723</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121369125</v>
+        <v>121368704</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>105210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581021</v>
+        <v>581129</v>
       </c>
       <c r="R2" t="n">
-        <v>6388049</v>
+        <v>6388103</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121367964</v>
+        <v>121368155</v>
       </c>
       <c r="B3" t="n">
-        <v>92029</v>
+        <v>105210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,45 +802,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581144</v>
+        <v>581151</v>
       </c>
       <c r="R3" t="n">
-        <v>6388089</v>
+        <v>6388061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1014,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368704</v>
+        <v>121367964</v>
       </c>
       <c r="B5" t="n">
-        <v>105210</v>
+        <v>92029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,42 +1024,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581129</v>
+        <v>581144</v>
       </c>
       <c r="R5" t="n">
-        <v>6388103</v>
+        <v>6388089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121368155</v>
+        <v>121369125</v>
       </c>
       <c r="B6" t="n">
-        <v>105210</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,49 +1134,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581151</v>
+        <v>581021</v>
       </c>
       <c r="R6" t="n">
-        <v>6388061</v>
+        <v>6388049</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368155</v>
+        <v>121369125</v>
       </c>
       <c r="B3" t="n">
-        <v>105210</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,49 +798,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581151</v>
+        <v>581021</v>
       </c>
       <c r="R3" t="n">
-        <v>6388061</v>
+        <v>6388049</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368303</v>
+        <v>121368155</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>105210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581122</v>
+        <v>581151</v>
       </c>
       <c r="R4" t="n">
-        <v>6388098</v>
+        <v>6388061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121367964</v>
+        <v>121368303</v>
       </c>
       <c r="B5" t="n">
-        <v>92029</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,49 +1023,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581144</v>
+        <v>581122</v>
       </c>
       <c r="R5" t="n">
-        <v>6388089</v>
+        <v>6388098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121369125</v>
+        <v>121367964</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>92029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,53 +1134,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581021</v>
+        <v>581144</v>
       </c>
       <c r="R6" t="n">
-        <v>6388049</v>
+        <v>6388089</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121368704</v>
+        <v>121369125</v>
       </c>
       <c r="B2" t="n">
-        <v>105210</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581129</v>
+        <v>581021</v>
       </c>
       <c r="R2" t="n">
-        <v>6388103</v>
+        <v>6388049</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121369125</v>
+        <v>121368155</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>105210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,53 +801,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581021</v>
+        <v>581151</v>
       </c>
       <c r="R3" t="n">
-        <v>6388049</v>
+        <v>6388061</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368155</v>
+        <v>121367964</v>
       </c>
       <c r="B4" t="n">
-        <v>105210</v>
+        <v>92029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,42 +916,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>a 54344,  Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581151</v>
+        <v>581144</v>
       </c>
       <c r="R4" t="n">
-        <v>6388061</v>
+        <v>6388089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368303</v>
+        <v>121368704</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>105210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1026,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,14 +1058,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581122</v>
+        <v>581129</v>
       </c>
       <c r="R5" t="n">
-        <v>6388098</v>
+        <v>6388103</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121367964</v>
+        <v>121368303</v>
       </c>
       <c r="B6" t="n">
-        <v>92029</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,49 +1137,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>a 54344,  Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581144</v>
+        <v>581122</v>
       </c>
       <c r="R6" t="n">
-        <v>6388089</v>
+        <v>6388098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54334-2024 artfynd.xlsx
+++ b/artfynd/A 54334-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121369125</v>
+        <v>121368303</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 54334, Örsviken, Sm</t>
+          <t>A 54344, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581021</v>
+        <v>581122</v>
       </c>
       <c r="R2" t="n">
-        <v>6388049</v>
+        <v>6388098</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368155</v>
+        <v>121369125</v>
       </c>
       <c r="B3" t="n">
-        <v>105210</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,49 +798,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 54344, Örsviken, Sm</t>
+          <t>A 54334, Örsviken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581151</v>
+        <v>581021</v>
       </c>
       <c r="R3" t="n">
-        <v>6388061</v>
+        <v>6388049</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,7 +903,7 @@
         <v>121367964</v>
       </c>
       <c r="B4" t="n">
-        <v>92029</v>
+        <v>92037</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>121368704</v>
       </c>
       <c r="B5" t="n">
-        <v>105210</v>
+        <v>105218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121368303</v>
+        <v>121368155</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>105218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581122</v>
+        <v>581151</v>
       </c>
       <c r="R6" t="n">
-        <v>6388098</v>
+        <v>6388061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>121368240</v>
       </c>
       <c r="B7" t="n">
-        <v>94723</v>
+        <v>94731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
